--- a/data/dividends_info_20260608.xlsx
+++ b/data/dividends_info_20260608.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K151"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>63.52000045776367</v>
+        <v>65.33999633789062</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1416876564096432</v>
+        <v>0.1377410545519254</v>
       </c>
       <c r="J2" t="n">
         <v>280</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>57.20000076293945</v>
+        <v>57.40000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.223776207453371</v>
+        <v>1.219512162703347</v>
       </c>
       <c r="J3" t="n">
         <v>259</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.020000457763672</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6651884363083036</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J4" t="n">
         <v>189</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>63.52000045776367</v>
+        <v>65.33999633789062</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1416876564096432</v>
+        <v>0.1377410545519254</v>
       </c>
       <c r="J6" t="n">
         <v>189</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.089999914169312</v>
+        <v>2.075000047683716</v>
       </c>
       <c r="I7" t="n">
-        <v>3.68421067761643</v>
+        <v>3.710843288218411</v>
       </c>
       <c r="J7" t="n">
         <v>168</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.53000068664551</v>
+        <v>23.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.147471279732002</v>
+        <v>1.148936170212766</v>
       </c>
       <c r="J8" t="n">
         <v>168</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.590000152587891</v>
+        <v>5.559999942779541</v>
       </c>
       <c r="I9" t="n">
-        <v>3.577817433643719</v>
+        <v>3.597122339177877</v>
       </c>
       <c r="J9" t="n">
         <v>161</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.300000190734863</v>
+        <v>7.349999904632568</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8219177867440579</v>
+        <v>0.8163265412042129</v>
       </c>
       <c r="J10" t="n">
         <v>133</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.360000133514404</v>
+        <v>5.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9328357976591388</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="J12" t="n">
         <v>119</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.960000038146973</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J13" t="n">
         <v>112</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.53000068664551</v>
+        <v>23.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.147471279732002</v>
+        <v>1.148936170212766</v>
       </c>
       <c r="J14" t="n">
         <v>105</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>63.52000045776367</v>
+        <v>65.33999633789062</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1416876564096432</v>
+        <v>0.1377410545519254</v>
       </c>
       <c r="J15" t="n">
         <v>105</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.900000095367432</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I16" t="n">
-        <v>5.08474568052218</v>
+        <v>5.136986167150362</v>
       </c>
       <c r="J16" t="n">
         <v>98</v>
@@ -1196,11 +1196,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.004</v>
+        <v>0.25</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1209,45 +1209,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>IT0004587470</t>
+          <t>IT0001207098</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.4799999892711639</v>
+        <v>23.02000045776367</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8333333519597853</v>
+        <v>1.08601214174036</v>
       </c>
       <c r="J17" t="n">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>79</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.038</v>
+        <v>0.195</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1256,45 +1256,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>IT0005187460</t>
+          <t>IT0005331019</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.960000038146973</v>
+        <v>29.64999961853027</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7661290263658259</v>
+        <v>0.6576728583771428</v>
       </c>
       <c r="J18" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.25</v>
+        <v>0.033</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1318,30 +1318,30 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>IT0004098510</t>
+          <t>IT0005089476</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.949999809265137</v>
+        <v>1.830000042915344</v>
       </c>
       <c r="I19" t="n">
-        <v>4.201680806959162</v>
+        <v>1.803278646235889</v>
       </c>
       <c r="J19" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1365,30 +1365,30 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IT0005285942</t>
+          <t>IT0005176406</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.289999961853027</v>
+        <v>5.239999771118164</v>
       </c>
       <c r="I20" t="n">
-        <v>3.263403292421668</v>
+        <v>5.534351386777195</v>
       </c>
       <c r="J20" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1412,30 +1412,30 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IT0003128367</t>
+          <t>IT0001250932</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.633000373840332</v>
+        <v>3.75600004196167</v>
       </c>
       <c r="I21" t="n">
-        <v>2.699055225888539</v>
+        <v>4.259850857627674</v>
       </c>
       <c r="J21" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6</v>
+        <v>0.1386</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1459,30 +1459,30 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IT0005221517</t>
+          <t>IT0003027817</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.72000026702881</v>
+        <v>2.661999940872192</v>
       </c>
       <c r="I22" t="n">
-        <v>4.076086882579305</v>
+        <v>5.206611685896143</v>
       </c>
       <c r="J22" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="K22" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.22</v>
+        <v>0.63</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1506,30 +1506,30 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NL0015001OJ9</t>
+          <t>IT0003856405</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.641999959945679</v>
+        <v>51.38999938964844</v>
       </c>
       <c r="I23" t="n">
-        <v>6.040637079064695</v>
+        <v>1.225919454139752</v>
       </c>
       <c r="J23" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.004</v>
+        <v>0.14</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1538,45 +1538,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>IT0004587470</t>
+          <t>IT0005043507</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.4799999892711639</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8333333519597853</v>
+        <v>2.314049513823154</v>
       </c>
       <c r="J24" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1</v>
+        <v>0.78</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1585,45 +1585,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IT0005278236</t>
+          <t>IT0005353815</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.03000020980835</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I25" t="n">
-        <v>1.658374735001515</v>
+        <v>4.193548301090768</v>
       </c>
       <c r="J25" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.376</v>
+        <v>0.85</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1647,77 +1647,77 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IT0000214293</t>
+          <t>IT0003796171</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.64999961853027</v>
+        <v>26.13999938964844</v>
       </c>
       <c r="I26" t="n">
-        <v>2.016085832122022</v>
+        <v>3.251721575542974</v>
       </c>
       <c r="J26" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>IT0004053440</t>
+          <t>NL0000226223</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.829999923706055</v>
+        <v>65.33999633789062</v>
       </c>
       <c r="I27" t="n">
-        <v>2.058319066387184</v>
+        <v>0.1377410545519254</v>
       </c>
       <c r="J27" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1741,30 +1741,30 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>IT0005605701</t>
+          <t>IT0005573123</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.300000190734863</v>
+        <v>1.429999947547913</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5376343975757395</v>
+        <v>0.699300724950897</v>
       </c>
       <c r="J28" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.15</v>
+        <v>0.1813</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1788,30 +1788,30 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>IT0005425365</t>
+          <t>IT0003153415</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.660000085830688</v>
+        <v>6.251999855041504</v>
       </c>
       <c r="I29" t="n">
-        <v>5.639097562403148</v>
+        <v>2.899872108183157</v>
       </c>
       <c r="J29" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1835,30 +1835,30 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>IT0001382024</t>
+          <t>IT0003153621</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.160000085830688</v>
+        <v>8.640000343322754</v>
       </c>
       <c r="I30" t="n">
-        <v>3.935185028814982</v>
+        <v>3.009259139682045</v>
       </c>
       <c r="J30" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0135</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1882,30 +1882,30 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>IT0005561441</t>
+          <t>IT0004412497</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.389999866485596</v>
+        <v>1.085000038146973</v>
       </c>
       <c r="I31" t="n">
-        <v>1.594533078107776</v>
+        <v>1.244239587590808</v>
       </c>
       <c r="J31" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1929,30 +1929,30 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>IT0004195308</t>
+          <t>IT0005383291</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>34.40000152587891</v>
+        <v>3.072000026702881</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4360464922862167</v>
+        <v>3.580729135541737</v>
       </c>
       <c r="J32" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.04</v>
+        <v>0.024</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1961,12 +1961,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1976,30 +1976,30 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>IT0005508574</t>
+          <t>IT0005670960</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.849999904632568</v>
+        <v>1.980000019073486</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6837606949074361</v>
+        <v>1.212121200444759</v>
       </c>
       <c r="J33" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2008,45 +2008,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IT0001207098</t>
+          <t>IT0004093263</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>23.13999938964844</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="I34" t="n">
-        <v>1.080380322360061</v>
+        <v>5.479451911627054</v>
       </c>
       <c r="J34" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.195</v>
+        <v>0.025</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2070,30 +2070,30 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>IT0005331019</t>
+          <t>IT0005433765</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29.70000076293945</v>
+        <v>0.8899999856948853</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6565656396996691</v>
+        <v>2.808988809194278</v>
       </c>
       <c r="J35" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.033</v>
+        <v>1.11</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2102,45 +2102,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>IT0005089476</t>
+          <t>NL0015000K93</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.830000042915344</v>
+        <v>26.89999961853027</v>
       </c>
       <c r="I36" t="n">
-        <v>1.803278646235889</v>
+        <v>4.126394110561131</v>
       </c>
       <c r="J36" t="n">
-        <v>14</v>
+        <v>-4</v>
       </c>
       <c r="K36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.29</v>
+        <v>0.03</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2164,30 +2164,30 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>IT0005176406</t>
+          <t>IT0001237053</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.269999980926514</v>
+        <v>0.8889999985694885</v>
       </c>
       <c r="I37" t="n">
-        <v>5.502846319726464</v>
+        <v>3.3745781831579</v>
       </c>
       <c r="J37" t="n">
-        <v>14</v>
+        <v>-7</v>
       </c>
       <c r="K37" t="n">
-        <v>16</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.16</v>
+        <v>0.023</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2196,12 +2196,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2211,30 +2211,30 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>IT0001250932</t>
+          <t>IT0000060886</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.809999942779541</v>
+        <v>0.4810000061988831</v>
       </c>
       <c r="I38" t="n">
-        <v>4.199475128686587</v>
+        <v>4.781704720080606</v>
       </c>
       <c r="J38" t="n">
-        <v>14</v>
+        <v>-7</v>
       </c>
       <c r="K38" t="n">
-        <v>16</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1386</v>
+        <v>0.6</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2258,30 +2258,30 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>IT0003027817</t>
+          <t>IT0005245508</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.676000118255615</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="I39" t="n">
-        <v>5.179371968426824</v>
+        <v>3.084832783879659</v>
       </c>
       <c r="J39" t="n">
-        <v>14</v>
+        <v>-7</v>
       </c>
       <c r="K39" t="n">
-        <v>16</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.63</v>
+        <v>0.2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2305,30 +2305,30 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>IT0003856405</t>
+          <t>IT0005469264</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>52.06000137329102</v>
+        <v>9.359999656677246</v>
       </c>
       <c r="I40" t="n">
-        <v>1.210142111758024</v>
+        <v>2.136752215127741</v>
       </c>
       <c r="J40" t="n">
-        <v>14</v>
+        <v>-7</v>
       </c>
       <c r="K40" t="n">
-        <v>16</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2352,30 +2352,30 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>IT0005043507</t>
+          <t>IT0004329733</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.074999809265137</v>
+        <v>2.434999942779541</v>
       </c>
       <c r="I41" t="n">
-        <v>2.304526821325697</v>
+        <v>7.392197298967114</v>
       </c>
       <c r="J41" t="n">
-        <v>14</v>
+        <v>-14</v>
       </c>
       <c r="K41" t="n">
-        <v>16</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.78</v>
+        <v>0.3</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2399,30 +2399,30 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>IT0005353815</t>
+          <t>IT0005600249</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>18.60000038146973</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I42" t="n">
-        <v>4.193548301090768</v>
+        <v>3.571428733618088</v>
       </c>
       <c r="J42" t="n">
-        <v>14</v>
+        <v>-14</v>
       </c>
       <c r="K42" t="n">
-        <v>16</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.85</v>
+        <v>0.25</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2431,12 +2431,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2446,77 +2446,77 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>IT0003796171</t>
+          <t>IT0005453250</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>26.32500076293945</v>
+        <v>15.80000019073486</v>
       </c>
       <c r="I43" t="n">
-        <v>3.228869801958893</v>
+        <v>1.582278461911667</v>
       </c>
       <c r="J43" t="n">
-        <v>14</v>
+        <v>-14</v>
       </c>
       <c r="K43" t="n">
-        <v>16</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>NL0000226223</t>
+          <t>IT0005588626</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>63.52000045776367</v>
+        <v>3.930000066757202</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1416876564096432</v>
+        <v>0.7633587656591105</v>
       </c>
       <c r="J44" t="n">
-        <v>14</v>
+        <v>-14</v>
       </c>
       <c r="K44" t="n">
-        <v>16</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2540,30 +2540,30 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>IT0005573123</t>
+          <t>IT0005275778</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.409999966621399</v>
+        <v>4.199999809265137</v>
       </c>
       <c r="I45" t="n">
-        <v>0.709219874945225</v>
+        <v>3.571428733618088</v>
       </c>
       <c r="J45" t="n">
-        <v>14</v>
+        <v>-14</v>
       </c>
       <c r="K45" t="n">
-        <v>16</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1813</v>
+        <v>0.58</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2572,12 +2572,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2587,30 +2587,30 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>IT0003153415</t>
+          <t>IT0001042610</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.315999984741211</v>
+        <v>12.64999961853027</v>
       </c>
       <c r="I46" t="n">
-        <v>2.870487657346448</v>
+        <v>4.584980375417487</v>
       </c>
       <c r="J46" t="n">
-        <v>14</v>
+        <v>-14</v>
       </c>
       <c r="K46" t="n">
-        <v>16</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.26</v>
+        <v>2</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2634,30 +2634,30 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>IT0003153621</t>
+          <t>IT0003261697</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.720000267028809</v>
+        <v>35.0099983215332</v>
       </c>
       <c r="I47" t="n">
-        <v>2.981651284840964</v>
+        <v>5.712653801442437</v>
       </c>
       <c r="J47" t="n">
-        <v>14</v>
+        <v>-21</v>
       </c>
       <c r="K47" t="n">
-        <v>16</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.277</v>
+        <v>0.1</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2681,30 +2681,30 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>IT0003242622</t>
+          <t>NL0015000N33</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.125</v>
+        <v>3.186000108718872</v>
       </c>
       <c r="I48" t="n">
-        <v>2.735802469135803</v>
+        <v>3.138731845185378</v>
       </c>
       <c r="J48" t="n">
-        <v>14</v>
+        <v>-21</v>
       </c>
       <c r="K48" t="n">
-        <v>16</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0135</v>
+        <v>0.14846</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2728,30 +2728,30 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>IT0004412497</t>
+          <t>IT0005119810</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.065000057220459</v>
+        <v>37.70000076293945</v>
       </c>
       <c r="I49" t="n">
-        <v>1.26760556569674</v>
+        <v>0.3937930954790375</v>
       </c>
       <c r="J49" t="n">
-        <v>7</v>
+        <v>-21</v>
       </c>
       <c r="K49" t="n">
-        <v>9</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.11</v>
+        <v>0.92</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2775,30 +2775,30 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>IT0005383291</t>
+          <t>IT0003188064</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.065999984741211</v>
+        <v>20.78000068664551</v>
       </c>
       <c r="I50" t="n">
-        <v>3.587736482304147</v>
+        <v>4.427333828680998</v>
       </c>
       <c r="J50" t="n">
-        <v>7</v>
+        <v>-21</v>
       </c>
       <c r="K50" t="n">
-        <v>9</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.024</v>
+        <v>0.3</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2822,30 +2822,30 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>IT0005670960</t>
+          <t>NL0015001KT6</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.980000019073486</v>
+        <v>11.17000007629395</v>
       </c>
       <c r="I51" t="n">
-        <v>1.212121200444759</v>
+        <v>2.685765424806836</v>
       </c>
       <c r="J51" t="n">
-        <v>7</v>
+        <v>-21</v>
       </c>
       <c r="K51" t="n">
-        <v>9</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.16</v>
+        <v>1.04</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2869,30 +2869,30 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>IT0004093263</t>
+          <t>IT0004764699</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.980000019073486</v>
+        <v>85.63999938964844</v>
       </c>
       <c r="I52" t="n">
-        <v>5.36912748241343</v>
+        <v>1.214385809682418</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.025</v>
+        <v>0.7</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2916,30 +2916,30 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>IT0005433765</t>
+          <t>IT0001347308</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8700000047683716</v>
+        <v>43.52999877929688</v>
       </c>
       <c r="I53" t="n">
-        <v>2.87356320264113</v>
+        <v>1.608086422306366</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2948,45 +2948,45 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>NL0015000K93</t>
+          <t>IT0001031084</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.04999923706055</v>
+        <v>57.40000152587891</v>
       </c>
       <c r="I54" t="n">
-        <v>4.103512130526112</v>
+        <v>3.832752511353377</v>
       </c>
       <c r="J54" t="n">
-        <v>-4</v>
+        <v>-21</v>
       </c>
       <c r="K54" t="n">
-        <v>24</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.03</v>
+        <v>0.86</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3010,30 +3010,30 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>IT0001237053</t>
+          <t>IT0005508921</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8939999938011169</v>
+        <v>10.10400009155273</v>
       </c>
       <c r="I55" t="n">
-        <v>3.35570472125461</v>
+        <v>8.511480524619031</v>
       </c>
       <c r="J55" t="n">
-        <v>-7</v>
+        <v>-21</v>
       </c>
       <c r="K55" t="n">
-        <v>-5</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.023</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3042,12 +3042,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3057,30 +3057,30 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>IT0000060886</t>
+          <t>IT0000066123</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4799999892711639</v>
+        <v>12.27000045776367</v>
       </c>
       <c r="I56" t="n">
-        <v>4.791666773768765</v>
+        <v>4.563977009843287</v>
       </c>
       <c r="J56" t="n">
-        <v>-7</v>
+        <v>-21</v>
       </c>
       <c r="K56" t="n">
-        <v>-5</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6</v>
+        <v>0.04</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3104,30 +3104,30 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>IT0005245508</t>
+          <t>IT0001472171</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19.5</v>
+        <v>2.269999980926514</v>
       </c>
       <c r="I57" t="n">
-        <v>3.076923076923077</v>
+        <v>1.762114552250955</v>
       </c>
       <c r="J57" t="n">
-        <v>-7</v>
+        <v>-21</v>
       </c>
       <c r="K57" t="n">
-        <v>-5</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3151,30 +3151,30 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>IT0005469264</t>
+          <t>IT0003127930</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.359999656677246</v>
+        <v>8.909999847412109</v>
       </c>
       <c r="I58" t="n">
-        <v>2.136752215127741</v>
+        <v>3.367003424664865</v>
       </c>
       <c r="J58" t="n">
-        <v>-7</v>
+        <v>-21</v>
       </c>
       <c r="K58" t="n">
-        <v>-5</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.18</v>
+        <v>0.108</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3198,30 +3198,30 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>IT0004329733</t>
+          <t>IT0005244618</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.420000076293945</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I59" t="n">
-        <v>7.438016294431566</v>
+        <v>4.909090802689231</v>
       </c>
       <c r="J59" t="n">
-        <v>-14</v>
+        <v>-21</v>
       </c>
       <c r="K59" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3</v>
+        <v>2.06</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3245,30 +3245,30 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>IT0005600249</t>
+          <t>IT0001128047</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.199999809265137</v>
+        <v>90</v>
       </c>
       <c r="I60" t="n">
-        <v>3.658536670464694</v>
+        <v>2.288888888888889</v>
       </c>
       <c r="J60" t="n">
-        <v>-14</v>
+        <v>-21</v>
       </c>
       <c r="K60" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3277,12 +3277,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3292,30 +3292,30 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>IT0005453250</t>
+          <t>IT0003121677</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>15.6899995803833</v>
+        <v>15.30000019073486</v>
       </c>
       <c r="I61" t="n">
-        <v>1.593371616864585</v>
+        <v>4.901960723204261</v>
       </c>
       <c r="J61" t="n">
-        <v>-14</v>
+        <v>-21</v>
       </c>
       <c r="K61" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3339,30 +3339,30 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>IT0005588626</t>
+          <t>NL0013995087</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.950000047683716</v>
+        <v>13.55000019073486</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7594936617175999</v>
+        <v>2.214022109056</v>
       </c>
       <c r="J62" t="n">
-        <v>-14</v>
+        <v>-21</v>
       </c>
       <c r="K62" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.15</v>
+        <v>0.85</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3386,30 +3386,30 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>IT0005275778</t>
+          <t>IT0005246191</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.150000095367432</v>
+        <v>50.59999847412109</v>
       </c>
       <c r="I63" t="n">
-        <v>3.614457748264686</v>
+        <v>1.679841947890027</v>
       </c>
       <c r="J63" t="n">
-        <v>-14</v>
+        <v>-21</v>
       </c>
       <c r="K63" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3433,30 +3433,30 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>IT0001042610</t>
+          <t>IT0003115950</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.64999961853027</v>
+        <v>35.7400016784668</v>
       </c>
       <c r="I64" t="n">
-        <v>4.584980375417487</v>
+        <v>2.378287521212181</v>
       </c>
       <c r="J64" t="n">
-        <v>-14</v>
+        <v>-21</v>
       </c>
       <c r="K64" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.104</v>
+        <v>1.3</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3480,14 +3480,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>IT0001233417</t>
+          <t>IT0003492391</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.246000051498413</v>
+        <v>70.30000305175781</v>
       </c>
       <c r="I65" t="n">
-        <v>4.630454034523137</v>
+        <v>1.849217558415873</v>
       </c>
       <c r="J65" t="n">
         <v>-21</v>
@@ -3499,11 +3499,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.29</v>
+        <v>0.6</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3527,14 +3527,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>IT0004056880</t>
+          <t>IT0001463063</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.53999996185303</v>
+        <v>6.940000057220459</v>
       </c>
       <c r="I66" t="n">
-        <v>2.751423159863232</v>
+        <v>8.645533069927756</v>
       </c>
       <c r="J66" t="n">
         <v>-21</v>
@@ -3546,11 +3546,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.077</v>
+        <v>0.47</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3569,19 +3569,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>IT0001469383</t>
+          <t>IT0005669558</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.089999914169312</v>
+        <v>6.5</v>
       </c>
       <c r="I67" t="n">
-        <v>3.68421067761643</v>
+        <v>7.230769230769231</v>
       </c>
       <c r="J67" t="n">
         <v>-21</v>
@@ -3593,11 +3593,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.64</v>
+        <v>0.2</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3616,19 +3616,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>IT0000062072</t>
+          <t>IT0005312027</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>39.61999893188477</v>
+        <v>5.559999942779541</v>
       </c>
       <c r="I68" t="n">
-        <v>4.13932368554454</v>
+        <v>3.597122339177877</v>
       </c>
       <c r="J68" t="n">
         <v>-21</v>
@@ -3640,11 +3640,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3668,14 +3668,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>IT0003261697</t>
+          <t>IT0001157020</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>35.2599983215332</v>
+        <v>24.5</v>
       </c>
       <c r="I69" t="n">
-        <v>5.672150014762209</v>
+        <v>4.081632653061225</v>
       </c>
       <c r="J69" t="n">
         <v>-21</v>
@@ -3687,11 +3687,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.1</v>
+        <v>0.215</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3715,14 +3715,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>NL0015000N33</t>
+          <t>IT0004356751</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.211999893188477</v>
+        <v>4.75</v>
       </c>
       <c r="I70" t="n">
-        <v>3.11332513466345</v>
+        <v>4.526315789473684</v>
       </c>
       <c r="J70" t="n">
         <v>-21</v>
@@ -3734,11 +3734,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.14846</v>
+        <v>0.27</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3757,19 +3757,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>IT0005119810</t>
+          <t>IT0003132476</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>38.40000152587891</v>
+        <v>23.5</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3866145679706507</v>
+        <v>1.148936170212766</v>
       </c>
       <c r="J71" t="n">
         <v>-21</v>
@@ -3781,11 +3781,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.92</v>
+        <v>0.2</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3809,14 +3809,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>IT0003188064</t>
+          <t>IT0005521247</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>20.78000068664551</v>
+        <v>9.760000228881836</v>
       </c>
       <c r="I72" t="n">
-        <v>4.427333828680998</v>
+        <v>2.04918027981351</v>
       </c>
       <c r="J72" t="n">
         <v>-21</v>
@@ -3828,11 +3828,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>NL0015001KT6</t>
+          <t>IT0004967292</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.14999961853027</v>
+        <v>8.510000228881836</v>
       </c>
       <c r="I73" t="n">
-        <v>2.690583051692913</v>
+        <v>2.820211440012318</v>
       </c>
       <c r="J73" t="n">
         <v>-21</v>
@@ -3875,11 +3875,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.04</v>
+        <v>0.79</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3903,14 +3903,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>IT0004764699</t>
+          <t>IT0000072170</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>84.44000244140625</v>
+        <v>21.1299991607666</v>
       </c>
       <c r="I74" t="n">
-        <v>1.231643735114369</v>
+        <v>3.738760205285965</v>
       </c>
       <c r="J74" t="n">
         <v>-21</v>
@@ -3922,11 +3922,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7</v>
+        <v>0.093</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3950,14 +3950,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>IT0001347308</t>
+          <t>IT0005345233</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>43.97999954223633</v>
+        <v>5.380000114440918</v>
       </c>
       <c r="I75" t="n">
-        <v>1.591632576821091</v>
+        <v>1.728624498545469</v>
       </c>
       <c r="J75" t="n">
         <v>-21</v>
@@ -3969,11 +3969,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2.2</v>
+        <v>0.06</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3997,14 +3997,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>IT0001031084</t>
+          <t>IT0005359101</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>57.20000076293945</v>
+        <v>7.349999904632568</v>
       </c>
       <c r="I76" t="n">
-        <v>3.846153794853453</v>
+        <v>0.8163265412042129</v>
       </c>
       <c r="J76" t="n">
         <v>-21</v>
@@ -4016,11 +4016,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.86</v>
+        <v>0.35</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4044,14 +4044,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>IT0005508921</t>
+          <t>IT0001078911</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>10.03999996185303</v>
+        <v>34.38000106811523</v>
       </c>
       <c r="I77" t="n">
-        <v>8.565737084338339</v>
+        <v>1.018033708918635</v>
       </c>
       <c r="J77" t="n">
         <v>-21</v>
@@ -4063,11 +4063,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5543</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4091,14 +4091,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>IT0000066123</t>
+          <t>IT0005090300</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>12.21599960327148</v>
+        <v>6.704999923706055</v>
       </c>
       <c r="I78" t="n">
-        <v>4.584152080768161</v>
+        <v>8.266965045595731</v>
       </c>
       <c r="J78" t="n">
         <v>-21</v>
@@ -4110,11 +4110,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4138,14 +4138,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>IT0001472171</t>
+          <t>IT0001077780</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.279999971389771</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I79" t="n">
-        <v>1.754385986926923</v>
+        <v>2.678571417167479</v>
       </c>
       <c r="J79" t="n">
         <v>-21</v>
@@ -4157,11 +4157,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4185,14 +4185,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>IT0003127930</t>
+          <t>IT0003411417</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>8.880000114440918</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="I80" t="n">
-        <v>3.378378334839559</v>
+        <v>1.418439677936752</v>
       </c>
       <c r="J80" t="n">
         <v>-21</v>
@@ -4204,11 +4204,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.108</v>
+        <v>0.103</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4232,14 +4232,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>IT0005244618</t>
+          <t>IT0005186371</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2.200000047683716</v>
+        <v>7.190000057220459</v>
       </c>
       <c r="I81" t="n">
-        <v>4.909090802689231</v>
+        <v>1.432545190268304</v>
       </c>
       <c r="J81" t="n">
         <v>-21</v>
@@ -4251,11 +4251,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2.06</v>
+        <v>0.19</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4279,14 +4279,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>IT0001128047</t>
+          <t>IT0000072618</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>88.40000152587891</v>
+        <v>5.59499979019165</v>
       </c>
       <c r="I82" t="n">
-        <v>2.33031670185768</v>
+        <v>3.395889314117236</v>
       </c>
       <c r="J82" t="n">
         <v>-21</v>
@@ -4298,11 +4298,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.75</v>
+        <v>0.432</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4326,14 +4326,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>IT0003121677</t>
+          <t>IT0005211237</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>15.38000011444092</v>
+        <v>10.22999954223633</v>
       </c>
       <c r="I83" t="n">
-        <v>4.876462902596431</v>
+        <v>4.222874089254971</v>
       </c>
       <c r="J83" t="n">
         <v>-21</v>
@@ -4345,11 +4345,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.3</v>
+        <v>0.44</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4373,14 +4373,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>NL0013995087</t>
+          <t>IT0005541336</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>13.86999988555908</v>
+        <v>26.03000068664551</v>
       </c>
       <c r="I84" t="n">
-        <v>2.162941618423145</v>
+        <v>1.690357235471525</v>
       </c>
       <c r="J84" t="n">
         <v>-21</v>
@@ -4392,11 +4392,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.85</v>
+        <v>0.03</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4420,14 +4420,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>IT0005246191</t>
+          <t>IT0004522162</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>50.40000152587891</v>
+        <v>1.039999961853027</v>
       </c>
       <c r="I85" t="n">
-        <v>1.686507885448278</v>
+        <v>2.88461549042245</v>
       </c>
       <c r="J85" t="n">
         <v>-21</v>
@@ -4439,11 +4439,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.85</v>
+        <v>0.47</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4467,14 +4467,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>IT0003115950</t>
+          <t>IT0003428445</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>35.54000091552734</v>
+        <v>6.769999980926514</v>
       </c>
       <c r="I86" t="n">
-        <v>2.391671294607753</v>
+        <v>6.942392929455781</v>
       </c>
       <c r="J86" t="n">
         <v>-21</v>
@@ -4486,11 +4486,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4514,14 +4514,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>IT0003492391</t>
+          <t>IT0004965148</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>70.76000213623047</v>
+        <v>54.77999877929688</v>
       </c>
       <c r="I87" t="n">
-        <v>1.837196100555762</v>
+        <v>2.555677311422476</v>
       </c>
       <c r="J87" t="n">
         <v>-21</v>
@@ -4533,11 +4533,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4561,14 +4561,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>IT0001463063</t>
+          <t>IT0005366767</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>6.900000095367432</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="I88" t="n">
-        <v>8.695652053727246</v>
+        <v>9.009009215415272</v>
       </c>
       <c r="J88" t="n">
         <v>-21</v>
@@ -4580,11 +4580,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.47</v>
+        <v>0.12</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4608,14 +4608,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>IT0005669558</t>
+          <t>IT0005594418</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>6.5</v>
+        <v>15.60000038146973</v>
       </c>
       <c r="I89" t="n">
-        <v>7.230769230769231</v>
+        <v>0.7692307504206254</v>
       </c>
       <c r="J89" t="n">
         <v>-21</v>
@@ -4627,11 +4627,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4650,19 +4650,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>IT0005312027</t>
+          <t>IT0005453748</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.590000152587891</v>
+        <v>3.430000066757202</v>
       </c>
       <c r="I90" t="n">
-        <v>3.577817433643719</v>
+        <v>4.95626812511178</v>
       </c>
       <c r="J90" t="n">
         <v>-21</v>
@@ -4674,11 +4674,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4702,14 +4702,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>IT0001157020</t>
+          <t>IT0005373789</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>24.52000045776367</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="I91" t="n">
-        <v>4.078303349637067</v>
+        <v>3.153153044789871</v>
       </c>
       <c r="J91" t="n">
         <v>-21</v>
@@ -4721,11 +4721,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.215</v>
+        <v>0.035</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4749,14 +4749,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>IT0004356751</t>
+          <t>IT0005378143</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4.739999771118164</v>
+        <v>2.579999923706055</v>
       </c>
       <c r="I92" t="n">
-        <v>4.535865197927669</v>
+        <v>1.356589187402923</v>
       </c>
       <c r="J92" t="n">
         <v>-21</v>
@@ -4768,11 +4768,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4791,19 +4791,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>IT0003132476</t>
+          <t>IT0005054967</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>23.53000068664551</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="I93" t="n">
-        <v>1.147471279732002</v>
+        <v>5.967450044842524</v>
       </c>
       <c r="J93" t="n">
         <v>-21</v>
@@ -4815,11 +4815,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4843,14 +4843,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IT0005521247</t>
+          <t>IT0004931496</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>10.19999980926514</v>
+        <v>0.9490000009536743</v>
       </c>
       <c r="I94" t="n">
-        <v>1.96078435039117</v>
+        <v>7.376185450964723</v>
       </c>
       <c r="J94" t="n">
         <v>-21</v>
@@ -4862,11 +4862,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.24</v>
+        <v>0.71</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>IT0004967292</t>
+          <t>IT0003828271</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>8.524999618530273</v>
+        <v>50.79999923706055</v>
       </c>
       <c r="I95" t="n">
-        <v>2.815249392836647</v>
+        <v>1.397637816266004</v>
       </c>
       <c r="J95" t="n">
         <v>-21</v>
@@ -4909,11 +4909,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.79</v>
+        <v>1.35</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>IT0000072170</t>
+          <t>IT0005282865</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>21.45999908447266</v>
+        <v>104.5999984741211</v>
       </c>
       <c r="I96" t="n">
-        <v>3.681267631421304</v>
+        <v>1.290630993970809</v>
       </c>
       <c r="J96" t="n">
         <v>-21</v>
@@ -4956,11 +4956,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.093</v>
+        <v>0.08</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4984,14 +4984,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>IT0005345233</t>
+          <t>IT0005543613</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.380000114440918</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="I97" t="n">
-        <v>1.728624498545469</v>
+        <v>1.095890382325411</v>
       </c>
       <c r="J97" t="n">
         <v>-21</v>
@@ -5003,11 +5003,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.06</v>
+        <v>3</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5026,19 +5026,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>IT0005359101</t>
+          <t>IT0001017851</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>7.300000190734863</v>
+        <v>258</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8219177867440579</v>
+        <v>1.162790697674419</v>
       </c>
       <c r="J98" t="n">
         <v>-21</v>
@@ -5050,11 +5050,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.35</v>
+        <v>0.17</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5078,14 +5078,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>IT0001078911</t>
+          <t>IT0005495657</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>34.13999938964844</v>
+        <v>4.448999881744385</v>
       </c>
       <c r="I99" t="n">
-        <v>1.025190410829718</v>
+        <v>3.821083491091162</v>
       </c>
       <c r="J99" t="n">
         <v>-21</v>
@@ -5097,11 +5097,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5543</v>
+        <v>0.297</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>IT0005090300</t>
+          <t>IT0005568461</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.71999979019165</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I100" t="n">
-        <v>8.248512162292668</v>
+        <v>4.013513461789396</v>
       </c>
       <c r="J100" t="n">
         <v>-21</v>
@@ -5144,11 +5144,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.06</v>
+        <v>0.45</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>IT0001077780</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.220000028610229</v>
+        <v>59.90000152587891</v>
       </c>
       <c r="I101" t="n">
-        <v>2.702702667871647</v>
+        <v>0.7512520676741289</v>
       </c>
       <c r="J101" t="n">
         <v>-21</v>
@@ -5191,11 +5191,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>IT0003411417</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>13.80000019073486</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="I102" t="n">
-        <v>1.449275342287875</v>
+        <v>0.704225373395827</v>
       </c>
       <c r="J102" t="n">
         <v>-21</v>
@@ -5238,11 +5238,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.103</v>
+        <v>1.05</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IT0005186371</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.15500020980835</v>
+        <v>38.18000030517578</v>
       </c>
       <c r="I103" t="n">
-        <v>1.439552718095013</v>
+        <v>2.750130936635061</v>
       </c>
       <c r="J103" t="n">
         <v>-21</v>
@@ -5285,11 +5285,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IT0000072618</t>
+          <t>IT0005621070</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.563000202178955</v>
+        <v>1.549999952316284</v>
       </c>
       <c r="I104" t="n">
-        <v>3.415423208605664</v>
+        <v>3.225806550850609</v>
       </c>
       <c r="J104" t="n">
         <v>-21</v>
@@ -5332,11 +5332,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.432</v>
+        <v>0.38</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5360,14 +5360,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>IT0005211237</t>
+          <t>IT0005162406</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>10.32499980926514</v>
+        <v>17.02000045776367</v>
       </c>
       <c r="I105" t="n">
-        <v>4.184019447751901</v>
+        <v>2.232667390009752</v>
       </c>
       <c r="J105" t="n">
         <v>-21</v>
@@ -5379,15 +5379,15 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>IT0005541336</t>
+          <t>LU2598331598</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>26.09000015258789</v>
+        <v>27.18000030517578</v>
       </c>
       <c r="I106" t="n">
-        <v>1.686469901980265</v>
+        <v>2.207505493978028</v>
       </c>
       <c r="J106" t="n">
         <v>-21</v>
@@ -5426,11 +5426,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.03</v>
+        <v>0.35</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>IT0004522162</t>
+          <t>IT0001454435</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>1.039999961853027</v>
+        <v>38</v>
       </c>
       <c r="I107" t="n">
-        <v>2.88461549042245</v>
+        <v>0.9210526315789472</v>
       </c>
       <c r="J107" t="n">
         <v>-21</v>
@@ -5473,11 +5473,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.47</v>
+        <v>0.017</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>IT0003428445</t>
+          <t>IT0005658841</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>6.849999904632568</v>
+        <v>3.220000028610229</v>
       </c>
       <c r="I108" t="n">
-        <v>6.861313964138086</v>
+        <v>0.527950305868081</v>
       </c>
       <c r="J108" t="n">
         <v>-21</v>
@@ -5520,11 +5520,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1.4</v>
+        <v>0.01</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>IT0004965148</t>
+          <t>IT0005573065</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>55.09999847412109</v>
+        <v>2.904999971389771</v>
       </c>
       <c r="I109" t="n">
-        <v>2.54083491609812</v>
+        <v>0.3442340825640675</v>
       </c>
       <c r="J109" t="n">
         <v>-21</v>
@@ -5567,11 +5567,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.3</v>
+        <v>1.12</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5595,14 +5595,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>IT0005366767</t>
+          <t>IT0004810054</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.325000047683716</v>
+        <v>21.81999969482422</v>
       </c>
       <c r="I110" t="n">
-        <v>9.02255626158526</v>
+        <v>5.132905662989849</v>
       </c>
       <c r="J110" t="n">
         <v>-21</v>
@@ -5614,11 +5614,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5642,14 +5642,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>IT0005594418</t>
+          <t>IT0004717200</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>15.5</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7741935483870968</v>
+        <v>7.518796749870864</v>
       </c>
       <c r="J111" t="n">
         <v>-21</v>
@@ -5661,11 +5661,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.17</v>
+        <v>0.081</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT0005453748</t>
+          <t>IT0003865588</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.430000066757202</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="I112" t="n">
-        <v>4.95626812511178</v>
+        <v>0.8785249203263056</v>
       </c>
       <c r="J112" t="n">
         <v>-21</v>
@@ -5708,11 +5708,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>IT0005373789</t>
+          <t>IT0005610958</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>22.25</v>
+        <v>2.194000005722046</v>
       </c>
       <c r="I113" t="n">
-        <v>3.146067415730337</v>
+        <v>4.20692797444292</v>
       </c>
       <c r="J113" t="n">
         <v>-21</v>
@@ -5755,11 +5755,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.035</v>
+        <v>0.35</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5783,30 +5783,30 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IT0005378143</t>
+          <t>IT0001006128</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.579999923706055</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I114" t="n">
-        <v>1.356589187402923</v>
+        <v>3.846153684924045</v>
       </c>
       <c r="J114" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="K114" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.33</v>
+        <v>0.096</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5815,12 +5815,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5830,30 +5830,30 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT0005054967</t>
+          <t>IT0005543332</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.599999904632568</v>
+        <v>6.300000190734863</v>
       </c>
       <c r="I115" t="n">
-        <v>5.892857243211904</v>
+        <v>1.52380947767562</v>
       </c>
       <c r="J115" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="K115" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5862,12 +5862,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5877,30 +5877,30 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>IT0004931496</t>
+          <t>IT0005416281</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.9459999799728394</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I116" t="n">
-        <v>7.399577323670744</v>
+        <v>4.838709826275912</v>
       </c>
       <c r="J116" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="K116" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.71</v>
+        <v>0.2</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5924,30 +5924,30 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>IT0003828271</t>
+          <t>IT0005037905</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>50.75</v>
+        <v>11.5</v>
       </c>
       <c r="I117" t="n">
-        <v>1.399014778325123</v>
+        <v>1.739130434782609</v>
       </c>
       <c r="J117" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="K117" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.35</v>
+        <v>0.06</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5956,45 +5956,45 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>IT0005282865</t>
+          <t>IT0005337818</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>103.3000030517578</v>
+        <v>9</v>
       </c>
       <c r="I118" t="n">
-        <v>1.306873146289832</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J118" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="K118" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6018,30 +6018,30 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>IT0005543613</t>
+          <t>IT0005075764</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>7.320000171661377</v>
+        <v>18.6200008392334</v>
       </c>
       <c r="I119" t="n">
-        <v>1.092896149233872</v>
+        <v>2.685284519141759</v>
       </c>
       <c r="J119" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="K119" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3</v>
+        <v>0.06</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6050,12 +6050,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6065,30 +6065,30 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>IT0001017851</t>
+          <t>IT0004376858</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>258</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="I120" t="n">
-        <v>1.162790697674419</v>
+        <v>2.631578980390385</v>
       </c>
       <c r="J120" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="K120" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6112,30 +6112,30 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>IT0005495657</t>
+          <t>IT0005138703</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.448999881744385</v>
+        <v>15.10000038146973</v>
       </c>
       <c r="I121" t="n">
-        <v>3.821083491091162</v>
+        <v>3.311258194493725</v>
       </c>
       <c r="J121" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="K121" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.297</v>
+        <v>0.1</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6144,12 +6144,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6159,30 +6159,30 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IT0005568461</t>
+          <t>IT0005430951</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>7.400000095367432</v>
+        <v>3.700000047683716</v>
       </c>
       <c r="I122" t="n">
-        <v>4.013513461789396</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J122" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="K122" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.45</v>
+        <v>0.11</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6206,1335 +6206,19 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>IT0001206769</t>
+          <t>IT0005339160</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>59.79999923706055</v>
+        <v>3.190000057220459</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7525083708046543</v>
+        <v>3.448275800215698</v>
       </c>
       <c r="J123" t="n">
-        <v>-21</v>
+        <v>-28</v>
       </c>
       <c r="K123" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>SYS-DAT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>IT0005595423</t>
-        </is>
-      </c>
-      <c r="H124" t="n">
-        <v>5.840000152587891</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0.6849314889533817</v>
-      </c>
-      <c r="J124" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K124" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>IT0003549422</t>
-        </is>
-      </c>
-      <c r="H125" t="n">
-        <v>38.18000030517578</v>
-      </c>
-      <c r="I125" t="n">
-        <v>2.750130936635061</v>
-      </c>
-      <c r="J125" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K125" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Smart Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>IT0005621070</t>
-        </is>
-      </c>
-      <c r="H126" t="n">
-        <v>1.600000023841858</v>
-      </c>
-      <c r="I126" t="n">
-        <v>3.124999953433872</v>
-      </c>
-      <c r="J126" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K126" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>TECHNOGYM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>IT0005162406</t>
-        </is>
-      </c>
-      <c r="H127" t="n">
-        <v>17.21999931335449</v>
-      </c>
-      <c r="I127" t="n">
-        <v>2.206736441071177</v>
-      </c>
-      <c r="J127" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K127" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>TENARIS S.A.</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>DOLLARI USA</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>LU2598331598</t>
-        </is>
-      </c>
-      <c r="H128" t="n">
-        <v>27.1200008392334</v>
-      </c>
-      <c r="I128" t="n">
-        <v>2.212389312068178</v>
-      </c>
-      <c r="J128" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K128" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>IT0001454435</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
-        <v>36.79999923706055</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0.9510869762397222</v>
-      </c>
-      <c r="J129" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K129" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>IT0005658841</t>
-        </is>
-      </c>
-      <c r="H130" t="n">
-        <v>3.220000028610229</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0.527950305868081</v>
-      </c>
-      <c r="J130" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K130" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>UNIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>IT0005573065</t>
-        </is>
-      </c>
-      <c r="H131" t="n">
-        <v>2.890000104904175</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0.3460207486854598</v>
-      </c>
-      <c r="J131" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K131" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Unipol S.p.A.</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>IT0004810054</t>
-        </is>
-      </c>
-      <c r="H132" t="n">
-        <v>21.1200008392334</v>
-      </c>
-      <c r="I132" t="n">
-        <v>5.30303009230682</v>
-      </c>
-      <c r="J132" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K132" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>IT0004717200</t>
-        </is>
-      </c>
-      <c r="H133" t="n">
-        <v>1.340000033378601</v>
-      </c>
-      <c r="I133" t="n">
-        <v>7.462686381273111</v>
-      </c>
-      <c r="J133" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K133" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>WEBUILD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>IT0003865588</t>
-        </is>
-      </c>
-      <c r="H134" t="n">
-        <v>9.520000457763672</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0.8508402952222922</v>
-      </c>
-      <c r="J134" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K134" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>doValue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>0.09229999999999999</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>IT0005610958</t>
-        </is>
-      </c>
-      <c r="H135" t="n">
-        <v>2.221999883651733</v>
-      </c>
-      <c r="I135" t="n">
-        <v>4.153915609046301</v>
-      </c>
-      <c r="J135" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K135" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>IT0001006128</t>
-        </is>
-      </c>
-      <c r="H136" t="n">
-        <v>9.119999885559082</v>
-      </c>
-      <c r="I136" t="n">
-        <v>3.837719346402645</v>
-      </c>
-      <c r="J136" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K136" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Ecomembrane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>IT0005543332</t>
-        </is>
-      </c>
-      <c r="H137" t="n">
-        <v>6.300000190734863</v>
-      </c>
-      <c r="I137" t="n">
-        <v>1.52380947767562</v>
-      </c>
-      <c r="J137" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K137" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>IT0005416281</t>
-        </is>
-      </c>
-      <c r="H138" t="n">
-        <v>6.150000095367432</v>
-      </c>
-      <c r="I138" t="n">
-        <v>4.878048704844394</v>
-      </c>
-      <c r="J138" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K138" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>IT0005037905</t>
-        </is>
-      </c>
-      <c r="H139" t="n">
-        <v>11.39999961853027</v>
-      </c>
-      <c r="I139" t="n">
-        <v>1.754386023617996</v>
-      </c>
-      <c r="J139" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K139" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Intred S.p.A.</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Interim</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>IT0005337818</t>
-        </is>
-      </c>
-      <c r="H140" t="n">
-        <v>9.020000457763672</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0.6651884363083036</v>
-      </c>
-      <c r="J140" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K140" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Italian Wine Brands S.p.A.</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>IT0005075764</t>
-        </is>
-      </c>
-      <c r="H141" t="n">
-        <v>18.60000038146973</v>
-      </c>
-      <c r="I141" t="n">
-        <v>2.688171987878697</v>
-      </c>
-      <c r="J141" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K141" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>IT0004376858</t>
-        </is>
-      </c>
-      <c r="H142" t="n">
-        <v>2.279999971389771</v>
-      </c>
-      <c r="I142" t="n">
-        <v>2.631578980390385</v>
-      </c>
-      <c r="J142" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K142" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Orsero S.p.A.</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>IT0005138703</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
-        <v>15.11999988555908</v>
-      </c>
-      <c r="I143" t="n">
-        <v>3.306878331907552</v>
-      </c>
-      <c r="J143" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K143" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>PLANETEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>IT0005430951</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
-        <v>3.700000047683716</v>
-      </c>
-      <c r="I144" t="n">
-        <v>2.702702667871647</v>
-      </c>
-      <c r="J144" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K144" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>PLC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>IT0005339160</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
-        <v>3.190000057220459</v>
-      </c>
-      <c r="I145" t="n">
-        <v>3.448275800215698</v>
-      </c>
-      <c r="J145" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K145" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Porto Aviation Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>IT0005545238</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>8.550000190734863</v>
-      </c>
-      <c r="I146" t="n">
-        <v>0.9941520246059123</v>
-      </c>
-      <c r="J146" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K146" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Racing Force S.p.A.</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>IT0005466963</t>
-        </is>
-      </c>
-      <c r="H147" t="n">
-        <v>4.880000114440918</v>
-      </c>
-      <c r="I147" t="n">
-        <v>1.946721265822835</v>
-      </c>
-      <c r="J147" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K147" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>IT0005521551</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
-        <v>1.330000042915344</v>
-      </c>
-      <c r="I148" t="n">
-        <v>2.255639024961259</v>
-      </c>
-      <c r="J148" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K148" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>T.P.S. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>IT0005246142</t>
-        </is>
-      </c>
-      <c r="H149" t="n">
-        <v>8.149999618530273</v>
-      </c>
-      <c r="I149" t="n">
-        <v>1.104294530215329</v>
-      </c>
-      <c r="J149" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K149" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>VALTECNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>IT0005532525</t>
-        </is>
-      </c>
-      <c r="H150" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I150" t="n">
-        <v>1.176470588235294</v>
-      </c>
-      <c r="J150" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K150" t="n">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>IT0004171440</t>
-        </is>
-      </c>
-      <c r="H151" t="n">
-        <v>7.150000095367432</v>
-      </c>
-      <c r="I151" t="n">
-        <v>3.076923035882762</v>
-      </c>
-      <c r="J151" t="n">
-        <v>-28</v>
-      </c>
-      <c r="K151" t="n">
         <v>-26</v>
       </c>
     </row>
@@ -9412,61 +8096,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Officina Stellare S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>